--- a/data/trans_camb/IP2002-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.11022754226084</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.25620908099023</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.118442711378653</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.47548440724442</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.9072590304966571</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.9887128014249763</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-4.671106147189072</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.838140988460951</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.5083092558596163</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.184630880086713</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.745325602594402</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.568647745656774</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>2.776695411513861</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.350215982834659</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.953547688714816</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.66313908189219</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.491450604519791</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.992671992440048</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.1645841416718236</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1862249723458513</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.590994438015315</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.6586595118761517</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.150416236499639</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1639206153593726</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5372288427777824</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.7172679103916207</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.09801063569064235</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.2654854338613989</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2601171412877761</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3836369472956191</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.6935641776762355</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.042394410561758</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2.111782322600518</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.576742404204455</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.744916487171199</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.016133518153648</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.727622575055663</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.94123463531502</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.064842698635215</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.48269545180087</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.889905858134669</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-4.204478550079586</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-6.072477761359853</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.627830395384715</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.700841907408665</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.776589687565434</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.898576227668117</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-6.481710817459015</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.219653277063338</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-1.593821880264807</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.355193201668881</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.6800717495021741</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.7024802383857722</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.827128006432029</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2306202815616875</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.6596052513506874</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.3634853330950106</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6130775565630432</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.28685475844797</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6381665381328266</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.6179751616571275</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.8677404487285388</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.740998804752829</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8728759296656152</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5785202422176975</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8082027268187656</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.438957114536196</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.2451512024044729</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.4186301003717233</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.01909535052349363</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1464718787834023</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.3160526529920542</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-5.598609470439967</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.37192473364992</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.7314183605807365</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.325763245017223</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-2.463971532925756</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-1.198002850859042</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-10.51303354947375</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.658484476060474</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.238641574958746</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.986439493111607</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.447253651622861</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.17207006612966</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>-1.338541885673776</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.2945154282098457</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.10449163265276</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.049242402667707</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.7352733131813344</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.551077988542501</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.6881354403573822</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.5373613515434391</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1863414477269764</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.5925283169027874</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4048355340031173</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.196834304854524</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.911830194934146</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8025212898722184</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.5956307291779325</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.3723495969848245</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6997714077178256</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.5411176688402558</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>-0.08126763147459388</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.00823792189374244</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2.593382109570972</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2.826828935749431</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1856133763507161</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.3595711745372967</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.116927385063588</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.931854187317707</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.918443413923496</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.27298075954816</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.9895945386928957</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2.805638620967825</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.188818791510278</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.942606064069885</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.218679424439479</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.136837925167731</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-5.750807376032839</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.622593369453341</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>5.117676603745626</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.186272589508251</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5.652334994453337</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>7.402413409104796</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.500940421110324</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>7.336523369719218</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.02787442521269503</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.9373182803327642</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.2025738607655617</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.1344176352924379</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1497492825386109</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.4245601143954308</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.8214910793860151</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.4502132560011127</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.716050346679869</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.49795823138414</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6394021773503403</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1858629817560601</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>4.293635690296109</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.878282766529154</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1.182065115590934</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.368665414868708</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.9238845106761645</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.839081230078161</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-2.096130219205043</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.373855395790045</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.5140820374156918</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.8226013985698402</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.8298914384855978</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.8497375741387245</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.914227186645468</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.378345641925977</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.588276730518647</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.236043002145366</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.282471103746334</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.635980902596479</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.06241911440905645</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.1488322891489101</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.446730022968794</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>3.074155196824961</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.6348910034693013</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.7166138397008206</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3016049935834295</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.3415659174489534</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.09199381345366643</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1472026526878395</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1319945624693192</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.1351510982169604</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5013135986979295</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5461357749963547</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2469723362437167</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2012052080210205</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3283593673236052</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.361000265847899</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.01954823751669403</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.04377608263582049</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.5442018380896428</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.6666419982260862</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.1140092561978998</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1283951830538885</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
